--- a/artfynd/A 66836-2021 artfynd.xlsx
+++ b/artfynd/A 66836-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 66836-2021 artfynd.xlsx
+++ b/artfynd/A 66836-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95026515</v>
+        <v>95026514</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>381167.9817109357</v>
+        <v>381168</v>
       </c>
       <c r="R2" t="n">
-        <v>6751882.706677942</v>
+        <v>6751883</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-07-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95030617</v>
+        <v>95026519</v>
       </c>
       <c r="B3" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>381015.7783540079</v>
+        <v>381072</v>
       </c>
       <c r="R3" t="n">
-        <v>6751738.217718256</v>
+        <v>6751807</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2021-07-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95030607</v>
+        <v>95026539</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>381129.5545178</v>
+        <v>381032</v>
       </c>
       <c r="R4" t="n">
-        <v>6751857.193885079</v>
+        <v>6751783</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2021-07-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95030634</v>
+        <v>95030644</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>381128.0607588682</v>
+        <v>381064</v>
       </c>
       <c r="R5" t="n">
-        <v>6751900.118066857</v>
+        <v>6751835</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2021-07-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>95030590</v>
+        <v>95026515</v>
       </c>
       <c r="B6" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>380926.6767634678</v>
+        <v>381168</v>
       </c>
       <c r="R6" t="n">
-        <v>6751613.055120376</v>
+        <v>6751883</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2021-07-20</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,27 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>95026544</v>
+        <v>95030590</v>
       </c>
       <c r="B7" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>381055.0218144279</v>
+        <v>380926</v>
       </c>
       <c r="R7" t="n">
-        <v>6751802.680721152</v>
+        <v>6751613</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1228,9 @@
           <t>2021-07-20</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,27 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>95030639</v>
+        <v>95030638</v>
       </c>
       <c r="B8" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>381125.2976074792</v>
+        <v>380948</v>
       </c>
       <c r="R8" t="n">
-        <v>6751861.233796991</v>
+        <v>6751653</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1325,9 @@
           <t>2021-07-20</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>95026514</v>
+        <v>95030645</v>
       </c>
       <c r="B9" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>381167.9817109357</v>
+        <v>381147</v>
       </c>
       <c r="R9" t="n">
-        <v>6751882.706677942</v>
+        <v>6751971</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,19 +1422,9 @@
           <t>2021-07-20</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,12 +1439,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1574,12 +1454,7 @@
         <v>95030648</v>
       </c>
       <c r="B10" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>380979.115500857</v>
+        <v>380979</v>
       </c>
       <c r="R10" t="n">
-        <v>6751648.81837205</v>
+        <v>6751649</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,19 +1519,9 @@
           <t>2021-07-20</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>95030644</v>
+        <v>95030631</v>
       </c>
       <c r="B11" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>381063.894787621</v>
+        <v>381064</v>
       </c>
       <c r="R11" t="n">
-        <v>6751834.540390267</v>
+        <v>6751835</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,19 +1616,9 @@
           <t>2021-07-20</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>95026539</v>
+        <v>95026547</v>
       </c>
       <c r="B12" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>381032.4193049537</v>
+        <v>380914</v>
       </c>
       <c r="R12" t="n">
-        <v>6751783.460388092</v>
+        <v>6751627</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,19 +1713,9 @@
           <t>2021-07-20</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,37 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>95026504</v>
+        <v>95026548</v>
       </c>
       <c r="B13" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>381062.8704641241</v>
+        <v>380914</v>
       </c>
       <c r="R13" t="n">
-        <v>6751818.496522898</v>
+        <v>6751627</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,19 +1810,9 @@
           <t>2021-07-20</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>95030631</v>
+        <v>95030607</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>381063.894787621</v>
+        <v>381129</v>
       </c>
       <c r="R14" t="n">
-        <v>6751834.540390267</v>
+        <v>6751857</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2092,19 +1907,9 @@
           <t>2021-07-20</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,37 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>95030638</v>
+        <v>95030611</v>
       </c>
       <c r="B15" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>380948.0312479039</v>
+        <v>381113</v>
       </c>
       <c r="R15" t="n">
-        <v>6751653.268975134</v>
+        <v>6751920</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2204,19 +2004,9 @@
           <t>2021-07-20</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,15 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>95026519</v>
+        <v>95030634</v>
       </c>
       <c r="B16" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2259,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>381072.2290247905</v>
+        <v>381128</v>
       </c>
       <c r="R16" t="n">
-        <v>6751806.49047274</v>
+        <v>6751900</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2316,19 +2101,9 @@
           <t>2021-07-20</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,27 +2118,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>95026552</v>
+        <v>95026504</v>
       </c>
       <c r="B17" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>381048.0835976036</v>
+        <v>381063</v>
       </c>
       <c r="R17" t="n">
-        <v>6751799.502146597</v>
+        <v>6751819</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,19 +2198,9 @@
           <t>2021-07-20</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2021-07-20</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,50 +2227,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104308002</v>
+        <v>95026527</v>
       </c>
       <c r="B18" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Örsjödammen, Vrm</t>
+          <t>Dundern, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>381226.035620259</v>
+        <v>381117</v>
       </c>
       <c r="R18" t="n">
-        <v>6752028.388610335</v>
+        <v>6751939</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2537,22 +2292,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-09-06</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-09-06</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2576,6 +2321,491 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>95026544</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Dundern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>381055</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6751802</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2021-07-20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2021-07-20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>95026552</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Dundern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>381048</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6751799</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2021-07-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2021-07-20</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>95030617</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Dundern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>381016</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6751738</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2021-07-20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2021-07-20</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>95030639</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Dundern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>381126</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6751861</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2021-07-20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2021-07-20</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>104308002</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79359</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>185</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Örsjödammen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>381226</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6752029</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-09-06</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-09-06</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 66836-2021 artfynd.xlsx
+++ b/artfynd/A 66836-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308002</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95026514</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95026519</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95026539</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95030644</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95026515</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95030590</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95030638</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95030645</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95030648</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95030631</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95026547</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95026548</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95030607</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95030611</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95030634</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95026504</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95026527</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95026544</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95026552</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95030617</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,8 +2916,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95030639</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>